--- a/Team-Data/2012-13/2-1-2012-13.xlsx
+++ b/Team-Data/2012-13/2-1-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -763,7 +830,7 @@
         <v>6</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
         <v>5</v>
@@ -775,25 +842,25 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>28</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>27</v>
       </c>
       <c r="AR2" t="n">
         <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
         <v>9</v>
@@ -808,10 +875,10 @@
         <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
         <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="H3" t="n">
         <v>49.2</v>
       </c>
       <c r="I3" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J3" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L3" t="n">
         <v>5.4</v>
@@ -873,28 +940,28 @@
         <v>16.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.33</v>
+        <v>0.332</v>
       </c>
       <c r="O3" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="P3" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="R3" t="n">
         <v>8.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T3" t="n">
-        <v>39.8</v>
+        <v>39.6</v>
       </c>
       <c r="U3" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="V3" t="n">
         <v>14.7</v>
@@ -903,34 +970,34 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y3" t="n">
         <v>4.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.3</v>
+        <v>95.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="AD3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF3" t="n">
         <v>16</v>
       </c>
-      <c r="AE3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>15</v>
-      </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -939,7 +1006,7 @@
         <v>16</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
         <v>7</v>
@@ -954,13 +1021,13 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
         <v>28</v>
@@ -972,7 +1039,7 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
         <v>14</v>
@@ -987,10 +1054,10 @@
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB3" t="n">
         <v>20</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -1025,46 +1092,46 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" t="n">
         <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>0.596</v>
+        <v>0.587</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="J4" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.445</v>
+        <v>0.443</v>
       </c>
       <c r="L4" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M4" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="N4" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="O4" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P4" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.746</v>
+        <v>0.75</v>
       </c>
       <c r="R4" t="n">
         <v>12.4</v>
@@ -1076,10 +1143,10 @@
         <v>41.8</v>
       </c>
       <c r="U4" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W4" t="n">
         <v>7.2</v>
@@ -1088,13 +1155,13 @@
         <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z4" t="n">
         <v>18.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB4" t="n">
         <v>95.8</v>
@@ -1106,7 +1173,7 @@
         <v>6</v>
       </c>
       <c r="AE4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF4" t="n">
         <v>10</v>
@@ -1115,7 +1182,7 @@
         <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
@@ -1124,16 +1191,16 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
         <v>7</v>
@@ -1154,13 +1221,13 @@
         <v>18</v>
       </c>
       <c r="AU4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
         <v>20</v>
@@ -1172,7 +1239,7 @@
         <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
         <v>17</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -1285,22 +1352,22 @@
         <v>-8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
         <v>29</v>
       </c>
       <c r="AF5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH5" t="n">
         <v>8</v>
       </c>
       <c r="AI5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ5" t="n">
         <v>18</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1333,7 +1400,7 @@
         <v>25</v>
       </c>
       <c r="AT5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU5" t="n">
         <v>30</v>
@@ -1342,7 +1409,7 @@
         <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX5" t="n">
         <v>5</v>
@@ -1351,7 +1418,7 @@
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -1389,61 +1456,61 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6" t="n">
         <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>0.609</v>
+        <v>0.622</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J6" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.44</v>
       </c>
       <c r="L6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="M6" t="n">
         <v>13.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.35</v>
+        <v>0.357</v>
       </c>
       <c r="O6" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="P6" t="n">
         <v>22.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.781</v>
+        <v>0.778</v>
       </c>
       <c r="R6" t="n">
         <v>12.5</v>
       </c>
       <c r="S6" t="n">
-        <v>31.2</v>
+        <v>31.5</v>
       </c>
       <c r="T6" t="n">
-        <v>43.7</v>
+        <v>44</v>
       </c>
       <c r="U6" t="n">
         <v>22.8</v>
       </c>
       <c r="V6" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W6" t="n">
         <v>7.2</v>
@@ -1455,28 +1522,28 @@
         <v>5.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG6" t="n">
         <v>8</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>9</v>
       </c>
       <c r="AH6" t="n">
         <v>13</v>
@@ -1497,16 +1564,16 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
         <v>8</v>
@@ -1515,28 +1582,28 @@
         <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AU6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
         <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
         <v>26</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" t="n">
         <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>0.277</v>
+        <v>0.283</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J7" t="n">
-        <v>84.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="K7" t="n">
         <v>0.423</v>
@@ -1601,16 +1668,16 @@
         <v>20.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O7" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P7" t="n">
         <v>22.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.756</v>
+        <v>0.753</v>
       </c>
       <c r="R7" t="n">
         <v>12.8</v>
@@ -1628,7 +1695,7 @@
         <v>14.7</v>
       </c>
       <c r="W7" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X7" t="n">
         <v>3.7</v>
@@ -1637,16 +1704,16 @@
         <v>7</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="AA7" t="n">
         <v>20.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>95.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.4</v>
+        <v>-5.1</v>
       </c>
       <c r="AD7" t="n">
         <v>6</v>
@@ -1679,22 +1746,22 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP7" t="n">
         <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
         <v>6</v>
       </c>
       <c r="AS7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT7" t="n">
         <v>21</v>
@@ -1706,7 +1773,7 @@
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX7" t="n">
         <v>30</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
         <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>0.426</v>
+        <v>0.413</v>
       </c>
       <c r="H8" t="n">
         <v>49.1</v>
       </c>
       <c r="I8" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J8" t="n">
-        <v>84.3</v>
+        <v>84.2</v>
       </c>
       <c r="K8" t="n">
         <v>0.453</v>
@@ -1780,55 +1847,55 @@
         <v>7</v>
       </c>
       <c r="M8" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.362</v>
+        <v>0.361</v>
       </c>
       <c r="O8" t="n">
         <v>17.3</v>
       </c>
       <c r="P8" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.797</v>
+        <v>0.796</v>
       </c>
       <c r="R8" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S8" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V8" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W8" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA8" t="n">
         <v>19.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>100.7</v>
+        <v>100.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.2</v>
+        <v>-2.4</v>
       </c>
       <c r="AD8" t="n">
         <v>6</v>
@@ -1846,7 +1913,7 @@
         <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ8" t="n">
         <v>4</v>
@@ -1855,7 +1922,7 @@
         <v>12</v>
       </c>
       <c r="AL8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AM8" t="n">
         <v>15</v>
@@ -1876,7 +1943,7 @@
         <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>14</v>
@@ -1885,28 +1952,28 @@
         <v>12</v>
       </c>
       <c r="AV8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
         <v>16</v>
       </c>
       <c r="AX8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY8" t="n">
         <v>8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA8" t="n">
         <v>22</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -1935,34 +2002,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>0.625</v>
+        <v>0.617</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="J9" t="n">
         <v>85</v>
       </c>
       <c r="K9" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L9" t="n">
         <v>6.4</v>
       </c>
       <c r="M9" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N9" t="n">
         <v>0.336</v>
@@ -1974,31 +2041,31 @@
         <v>26</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="S9" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T9" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="U9" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V9" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W9" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X9" t="n">
         <v>6.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Z9" t="n">
         <v>20.6</v>
@@ -2007,22 +2074,22 @@
         <v>22.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>104</v>
+        <v>103.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
       </c>
       <c r="AF9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH9" t="n">
         <v>19</v>
@@ -2040,7 +2107,7 @@
         <v>21</v>
       </c>
       <c r="AM9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN9" t="n">
         <v>27</v>
@@ -2061,16 +2128,16 @@
         <v>10</v>
       </c>
       <c r="AT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" t="n">
         <v>3</v>
       </c>
-      <c r="AU9" t="n">
-        <v>2</v>
-      </c>
       <c r="AV9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AW9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" t="n">
         <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.383</v>
+        <v>0.37</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="J10" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K10" t="n">
-        <v>0.446</v>
+        <v>0.443</v>
       </c>
       <c r="L10" t="n">
         <v>6.2</v>
@@ -2147,37 +2214,37 @@
         <v>16.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O10" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P10" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.695</v>
+        <v>0.702</v>
       </c>
       <c r="R10" t="n">
         <v>12.7</v>
       </c>
       <c r="S10" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U10" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W10" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y10" t="n">
         <v>5.5</v>
@@ -2186,13 +2253,13 @@
         <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>95</v>
+        <v>94.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.7</v>
+        <v>-2.1</v>
       </c>
       <c r="AD10" t="n">
         <v>6</v>
@@ -2207,16 +2274,16 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="n">
         <v>23</v>
@@ -2228,28 +2295,28 @@
         <v>8</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR10" t="n">
         <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
         <v>28</v>
@@ -2261,16 +2328,16 @@
         <v>19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>1.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF11" t="n">
         <v>7</v>
@@ -2389,16 +2456,16 @@
         <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2410,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2431,7 +2498,7 @@
         <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW11" t="n">
         <v>26</v>
@@ -2449,10 +2516,10 @@
         <v>23</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -2562,22 +2629,22 @@
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG12" t="n">
         <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
         <v>7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK12" t="n">
         <v>10</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
@@ -2598,10 +2665,10 @@
         <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2610,7 +2677,7 @@
         <v>11</v>
       </c>
       <c r="AU12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2622,13 +2689,13 @@
         <v>27</v>
       </c>
       <c r="AY12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB12" t="n">
         <v>2</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F13" t="n">
         <v>19</v>
       </c>
       <c r="G13" t="n">
-        <v>0.596</v>
+        <v>0.587</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J13" t="n">
-        <v>81</v>
+        <v>81.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.428</v>
+        <v>0.426</v>
       </c>
       <c r="L13" t="n">
         <v>6.7</v>
@@ -2693,7 +2760,7 @@
         <v>19.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
       <c r="O13" t="n">
         <v>16</v>
@@ -2702,49 +2769,49 @@
         <v>21.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="R13" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S13" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T13" t="n">
-        <v>45.6</v>
+        <v>45.8</v>
       </c>
       <c r="U13" t="n">
         <v>19.9</v>
       </c>
       <c r="V13" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W13" t="n">
         <v>6.8</v>
       </c>
       <c r="X13" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="Y13" t="n">
         <v>5.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA13" t="n">
         <v>20.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>92</v>
+        <v>91.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="n">
         <v>6</v>
       </c>
       <c r="AE13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF13" t="n">
         <v>10</v>
@@ -2753,13 +2820,13 @@
         <v>10</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
@@ -2777,7 +2844,7 @@
         <v>22</v>
       </c>
       <c r="AP13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ13" t="n">
         <v>21</v>
@@ -2786,16 +2853,16 @@
         <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW13" t="n">
         <v>27</v>
@@ -2804,13 +2871,13 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -2845,58 +2912,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E14" t="n">
         <v>34</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.708</v>
+        <v>0.723</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.1</v>
+        <v>38.4</v>
       </c>
       <c r="J14" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.471</v>
+        <v>0.473</v>
       </c>
       <c r="L14" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M14" t="n">
         <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O14" t="n">
         <v>17.1</v>
       </c>
       <c r="P14" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.706</v>
+        <v>0.707</v>
       </c>
       <c r="R14" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S14" t="n">
         <v>30.3</v>
       </c>
       <c r="T14" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U14" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="V14" t="n">
         <v>14.3</v>
@@ -2911,19 +2978,19 @@
         <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>100.3</v>
+        <v>100.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2938,25 +3005,25 @@
         <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM14" t="n">
         <v>12</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP14" t="n">
         <v>8</v>
@@ -2968,10 +3035,10 @@
         <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
@@ -2989,13 +3056,13 @@
         <v>7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
         <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>0.447</v>
+        <v>0.435</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,16 +3112,16 @@
         <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>81.5</v>
+        <v>81.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L15" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="N15" t="n">
         <v>0.356</v>
@@ -3063,28 +3130,28 @@
         <v>19.1</v>
       </c>
       <c r="P15" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S15" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="T15" t="n">
-        <v>45.3</v>
+        <v>45</v>
       </c>
       <c r="U15" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V15" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W15" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X15" t="n">
         <v>5.5</v>
@@ -3093,16 +3160,16 @@
         <v>4.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.4</v>
+        <v>102.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AD15" t="n">
         <v>6</v>
@@ -3111,7 +3178,7 @@
         <v>18</v>
       </c>
       <c r="AF15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG15" t="n">
         <v>18</v>
@@ -3126,16 +3193,16 @@
         <v>20</v>
       </c>
       <c r="AK15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO15" t="n">
         <v>4</v>
@@ -3153,10 +3220,10 @@
         <v>3</v>
       </c>
       <c r="AT15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV15" t="n">
         <v>27</v>
@@ -3177,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="BB15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC15" t="n">
         <v>11</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16" t="n">
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.652</v>
+        <v>0.644</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,7 +3294,7 @@
         <v>36.2</v>
       </c>
       <c r="J16" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K16" t="n">
         <v>0.435</v>
@@ -3236,10 +3303,10 @@
         <v>4.7</v>
       </c>
       <c r="M16" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.338</v>
+        <v>0.34</v>
       </c>
       <c r="O16" t="n">
         <v>16.2</v>
@@ -3248,19 +3315,19 @@
         <v>20.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R16" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="S16" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T16" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U16" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V16" t="n">
         <v>14.8</v>
@@ -3272,22 +3339,22 @@
         <v>5.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA16" t="n">
         <v>19.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.09999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3341,22 +3408,22 @@
         <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB16" t="n">
         <v>28</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -3391,43 +3458,43 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" t="n">
         <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>0.674</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H17" t="n">
         <v>48.7</v>
       </c>
       <c r="I17" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J17" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0.489</v>
       </c>
       <c r="L17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M17" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.385</v>
+        <v>0.386</v>
       </c>
       <c r="O17" t="n">
         <v>17.1</v>
       </c>
       <c r="P17" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q17" t="n">
         <v>0.756</v>
@@ -3436,16 +3503,16 @@
         <v>8.5</v>
       </c>
       <c r="S17" t="n">
-        <v>30.6</v>
+        <v>30.9</v>
       </c>
       <c r="T17" t="n">
-        <v>39.1</v>
+        <v>39.4</v>
       </c>
       <c r="U17" t="n">
         <v>22.4</v>
       </c>
       <c r="V17" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W17" t="n">
         <v>8.300000000000001</v>
@@ -3457,22 +3524,22 @@
         <v>3.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB17" t="n">
-        <v>102.4</v>
+        <v>102.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AD17" t="n">
         <v>29</v>
       </c>
       <c r="AE17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>3</v>
@@ -3487,7 +3554,7 @@
         <v>3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK17" t="n">
         <v>1</v>
@@ -3502,19 +3569,19 @@
         <v>2</v>
       </c>
       <c r="AO17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP17" t="n">
         <v>12</v>
       </c>
-      <c r="AP17" t="n">
-        <v>11</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
       </c>
       <c r="AS17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3535,13 +3602,13 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
         <v>13</v>
       </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -3573,67 +3640,67 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" t="n">
         <v>24</v>
       </c>
       <c r="F18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>0.533</v>
+        <v>0.545</v>
       </c>
       <c r="H18" t="n">
         <v>48.2</v>
       </c>
       <c r="I18" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J18" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L18" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M18" t="n">
         <v>18.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O18" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P18" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R18" t="n">
         <v>13.1</v>
       </c>
       <c r="S18" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T18" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U18" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V18" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W18" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X18" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="Y18" t="n">
         <v>4.3</v>
@@ -3642,16 +3709,16 @@
         <v>19.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.5</v>
+        <v>97.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
@@ -3660,7 +3727,7 @@
         <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
         <v>25</v>
@@ -3675,22 +3742,22 @@
         <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
         <v>21</v>
       </c>
       <c r="AN18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR18" t="n">
         <v>4</v>
@@ -3699,16 +3766,16 @@
         <v>16</v>
       </c>
       <c r="AT18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW18" t="n">
         <v>6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7</v>
       </c>
       <c r="AX18" t="n">
         <v>1</v>
@@ -3717,13 +3784,13 @@
         <v>6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC18" t="n">
         <v>15</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -3755,55 +3822,55 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E19" t="n">
         <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>0.395</v>
+        <v>0.405</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J19" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="L19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M19" t="n">
         <v>18.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3</v>
+        <v>0.295</v>
       </c>
       <c r="O19" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="P19" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.729</v>
+        <v>0.733</v>
       </c>
       <c r="R19" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="S19" t="n">
         <v>30.7</v>
       </c>
       <c r="T19" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U19" t="n">
         <v>21.8</v>
@@ -3824,19 +3891,19 @@
         <v>18</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.4</v>
+        <v>-2.2</v>
       </c>
       <c r="AD19" t="n">
         <v>29</v>
       </c>
       <c r="AE19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF19" t="n">
         <v>18</v>
@@ -3851,7 +3918,7 @@
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -3860,7 +3927,7 @@
         <v>27</v>
       </c>
       <c r="AM19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AN19" t="n">
         <v>30</v>
@@ -3878,22 +3945,22 @@
         <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU19" t="n">
         <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>17</v>
       </c>
       <c r="AX19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
         <v>23</v>
@@ -3905,10 +3972,10 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E20" t="n">
         <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>0.319</v>
+        <v>0.326</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3955,46 +4022,46 @@
         <v>36</v>
       </c>
       <c r="J20" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="K20" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M20" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O20" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="P20" t="n">
         <v>19.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
         <v>30.2</v>
       </c>
       <c r="T20" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U20" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="W20" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X20" t="n">
         <v>5.3</v>
@@ -4003,16 +4070,16 @@
         <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>-4.1</v>
+        <v>-3.8</v>
       </c>
       <c r="AD20" t="n">
         <v>6</v>
@@ -4027,19 +4094,19 @@
         <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI20" t="n">
         <v>22</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL20" t="n">
         <v>13</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>14</v>
       </c>
       <c r="AM20" t="n">
         <v>19</v>
@@ -4048,13 +4115,13 @@
         <v>7</v>
       </c>
       <c r="AO20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
         <v>16</v>
@@ -4069,13 +4136,13 @@
         <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AW20" t="n">
         <v>29</v>
       </c>
       <c r="AX20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY20" t="n">
         <v>24</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F21" t="n">
         <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>0.659</v>
+        <v>0.651</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J21" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K21" t="n">
         <v>0.445</v>
@@ -4146,16 +4213,16 @@
         <v>11</v>
       </c>
       <c r="M21" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="N21" t="n">
         <v>0.383</v>
       </c>
       <c r="O21" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P21" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Q21" t="n">
         <v>0.752</v>
@@ -4164,19 +4231,19 @@
         <v>10.8</v>
       </c>
       <c r="S21" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="U21" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V21" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="W21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X21" t="n">
         <v>3.9</v>
@@ -4185,22 +4252,22 @@
         <v>3.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD21" t="n">
         <v>28</v>
       </c>
       <c r="AE21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF21" t="n">
         <v>5</v>
@@ -4215,10 +4282,10 @@
         <v>15</v>
       </c>
       <c r="AJ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4233,28 +4300,28 @@
         <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ21" t="n">
         <v>17</v>
       </c>
       <c r="AR21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT21" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>29</v>
@@ -4263,7 +4330,7 @@
         <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA21" t="n">
         <v>18</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>8.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4394,10 +4461,10 @@
         <v>9</v>
       </c>
       <c r="AI22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4424,7 +4491,7 @@
         <v>24</v>
       </c>
       <c r="AS22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
         <v>11</v>
@@ -4442,10 +4509,10 @@
         <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA22" t="n">
         <v>6</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E23" t="n">
         <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G23" t="n">
-        <v>0.304</v>
+        <v>0.311</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
@@ -4501,67 +4568,67 @@
         <v>37.7</v>
       </c>
       <c r="J23" t="n">
-        <v>83</v>
+        <v>82.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.349</v>
+        <v>0.353</v>
       </c>
       <c r="O23" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="P23" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.789</v>
+        <v>0.787</v>
       </c>
       <c r="R23" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S23" t="n">
         <v>32</v>
       </c>
       <c r="T23" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U23" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V23" t="n">
         <v>14.6</v>
       </c>
       <c r="W23" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="X23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
         <v>4.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AC23" t="n">
-        <v>-4.4</v>
+        <v>-4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE23" t="n">
         <v>27</v>
@@ -4579,7 +4646,7 @@
         <v>8</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AK23" t="n">
         <v>11</v>
@@ -4591,7 +4658,7 @@
         <v>13</v>
       </c>
       <c r="AN23" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4612,10 +4679,10 @@
         <v>13</v>
       </c>
       <c r="AU23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4627,13 +4694,13 @@
         <v>14</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F24" t="n">
         <v>26</v>
       </c>
       <c r="G24" t="n">
-        <v>0.435</v>
+        <v>0.422</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4683,46 +4750,46 @@
         <v>37.4</v>
       </c>
       <c r="J24" t="n">
-        <v>83.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L24" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M24" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.358</v>
+        <v>0.36</v>
       </c>
       <c r="O24" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="P24" t="n">
         <v>16.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="R24" t="n">
         <v>10.6</v>
       </c>
       <c r="S24" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T24" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U24" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="W24" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X24" t="n">
         <v>5.1</v>
@@ -4734,22 +4801,22 @@
         <v>18.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>93.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.2</v>
+        <v>-3.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE24" t="n">
         <v>19</v>
       </c>
       <c r="AF24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG24" t="n">
         <v>19</v>
@@ -4758,13 +4825,13 @@
         <v>20</v>
       </c>
       <c r="AI24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4773,7 +4840,7 @@
         <v>24</v>
       </c>
       <c r="AN24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4788,28 +4855,28 @@
         <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU24" t="n">
         <v>15</v>
       </c>
       <c r="AV24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY24" t="n">
         <v>9</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
         <v>16</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>0.34</v>
+        <v>0.348</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
@@ -4865,7 +4932,7 @@
         <v>37.4</v>
       </c>
       <c r="J25" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K25" t="n">
         <v>0.445</v>
@@ -4877,13 +4944,13 @@
         <v>17.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0.329</v>
+        <v>0.33</v>
       </c>
       <c r="O25" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="P25" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="Q25" t="n">
         <v>0.751</v>
@@ -4892,25 +4959,25 @@
         <v>11.1</v>
       </c>
       <c r="S25" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T25" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="U25" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V25" t="n">
         <v>14.2</v>
       </c>
       <c r="W25" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X25" t="n">
         <v>5.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z25" t="n">
         <v>20.5</v>
@@ -4919,34 +4986,34 @@
         <v>18.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-4.1</v>
+        <v>-4</v>
       </c>
       <c r="AD25" t="n">
         <v>6</v>
       </c>
       <c r="AE25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG25" t="n">
         <v>24</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>25</v>
       </c>
       <c r="AH25" t="n">
         <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL25" t="n">
         <v>25</v>
@@ -4958,10 +5025,10 @@
         <v>29</v>
       </c>
       <c r="AO25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ25" t="n">
         <v>19</v>
@@ -4973,7 +5040,7 @@
         <v>27</v>
       </c>
       <c r="AT25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU25" t="n">
         <v>17</v>
@@ -4985,10 +5052,10 @@
         <v>15</v>
       </c>
       <c r="AX25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -5029,43 +5096,43 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26" t="n">
         <v>23</v>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5</v>
+        <v>0.511</v>
       </c>
       <c r="H26" t="n">
         <v>48.8</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="J26" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L26" t="n">
         <v>8.1</v>
       </c>
       <c r="M26" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="N26" t="n">
         <v>0.337</v>
       </c>
       <c r="O26" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P26" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q26" t="n">
         <v>0.776</v>
@@ -5074,19 +5141,19 @@
         <v>11.7</v>
       </c>
       <c r="S26" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T26" t="n">
         <v>42</v>
       </c>
       <c r="U26" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V26" t="n">
         <v>15</v>
       </c>
       <c r="W26" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X26" t="n">
         <v>4.8</v>
@@ -5095,19 +5162,19 @@
         <v>4</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA26" t="n">
         <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2</v>
+        <v>-1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
@@ -5122,7 +5189,7 @@
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ26" t="n">
         <v>14</v>
@@ -5140,7 +5207,7 @@
         <v>26</v>
       </c>
       <c r="AO26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP26" t="n">
         <v>19</v>
@@ -5152,10 +5219,10 @@
         <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
         <v>22</v>
@@ -5164,25 +5231,25 @@
         <v>19</v>
       </c>
       <c r="AW26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA26" t="n">
         <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -5211,55 +5278,55 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E27" t="n">
         <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" t="n">
-        <v>0.354</v>
+        <v>0.362</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J27" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L27" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M27" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0.354</v>
+        <v>0.357</v>
       </c>
       <c r="O27" t="n">
         <v>17</v>
       </c>
       <c r="P27" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q27" t="n">
         <v>0.753</v>
       </c>
       <c r="R27" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S27" t="n">
         <v>28.5</v>
       </c>
       <c r="T27" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U27" t="n">
         <v>19.8</v>
@@ -5268,37 +5335,37 @@
         <v>14.9</v>
       </c>
       <c r="W27" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.6</v>
+        <v>-6.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
         <v>23</v>
@@ -5307,37 +5374,37 @@
         <v>19</v>
       </c>
       <c r="AJ27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK27" t="n">
         <v>22</v>
       </c>
       <c r="AL27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AN27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO27" t="n">
         <v>15</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>14</v>
       </c>
       <c r="AP27" t="n">
         <v>13</v>
       </c>
       <c r="AQ27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR27" t="n">
         <v>12</v>
       </c>
       <c r="AS27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT27" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AU27" t="n">
         <v>28</v>
@@ -5346,19 +5413,19 @@
         <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AX27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB27" t="n">
         <v>16</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5571,7 @@
         <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
         <v>23</v>
@@ -5531,7 +5598,7 @@
         <v>4</v>
       </c>
       <c r="AX28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F29" t="n">
         <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>0.362</v>
+        <v>0.348</v>
       </c>
       <c r="H29" t="n">
         <v>49</v>
@@ -5599,34 +5666,34 @@
         <v>0.444</v>
       </c>
       <c r="L29" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M29" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.352</v>
+        <v>0.349</v>
       </c>
       <c r="O29" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P29" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.769</v>
+        <v>0.772</v>
       </c>
       <c r="R29" t="n">
         <v>10.8</v>
       </c>
       <c r="S29" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T29" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="U29" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V29" t="n">
         <v>12.9</v>
@@ -5635,7 +5702,7 @@
         <v>7.2</v>
       </c>
       <c r="X29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y29" t="n">
         <v>5.2</v>
@@ -5644,55 +5711,55 @@
         <v>22.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB29" t="n">
         <v>97.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.5</v>
+        <v>-2.1</v>
       </c>
       <c r="AD29" t="n">
         <v>6</v>
       </c>
       <c r="AE29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF29" t="n">
         <v>23</v>
       </c>
       <c r="AG29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH29" t="n">
         <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ29" t="n">
         <v>15</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
         <v>22</v>
@@ -5704,31 +5771,31 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AV29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -5757,70 +5824,70 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
         <v>21</v>
       </c>
       <c r="G30" t="n">
-        <v>0.553</v>
+        <v>0.543</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J30" t="n">
         <v>81.7</v>
       </c>
       <c r="K30" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L30" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M30" t="n">
         <v>17</v>
       </c>
       <c r="N30" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O30" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="P30" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R30" t="n">
         <v>12.3</v>
       </c>
       <c r="S30" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="T30" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U30" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V30" t="n">
         <v>14.8</v>
       </c>
       <c r="W30" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X30" t="n">
         <v>6.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
         <v>21.6</v>
@@ -5829,34 +5896,34 @@
         <v>20.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>98</v>
+        <v>98.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="AD30" t="n">
         <v>6</v>
       </c>
       <c r="AE30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI30" t="n">
         <v>17</v>
       </c>
       <c r="AJ30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5880,16 +5947,16 @@
         <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU30" t="n">
         <v>8</v>
       </c>
       <c r="AV30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW30" t="n">
         <v>8</v>
@@ -5898,10 +5965,10 @@
         <v>6</v>
       </c>
       <c r="AY30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA30" t="n">
         <v>8</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" t="n">
         <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G31" t="n">
-        <v>0.244</v>
+        <v>0.25</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
@@ -5969,55 +6036,55 @@
         <v>19.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.338</v>
+        <v>0.34</v>
       </c>
       <c r="O31" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="P31" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="R31" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S31" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="T31" t="n">
-        <v>43.5</v>
+        <v>43.8</v>
       </c>
       <c r="U31" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V31" t="n">
         <v>15.5</v>
       </c>
       <c r="W31" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB31" t="n">
-        <v>90.90000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>-5</v>
+        <v>-4.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6035,7 +6102,7 @@
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
@@ -6044,40 +6111,40 @@
         <v>20</v>
       </c>
       <c r="AM31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN31" t="n">
         <v>24</v>
       </c>
       <c r="AO31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR31" t="n">
         <v>18</v>
       </c>
       <c r="AS31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU31" t="n">
         <v>20</v>
       </c>
       <c r="AV31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AW31" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY31" t="n">
         <v>15</v>
@@ -6086,7 +6153,7 @@
         <v>19</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB31" t="n">
         <v>30</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-1-2012-13</t>
+          <t>2013-02-01</t>
         </is>
       </c>
     </row>
